--- a/artfynd/A 21511-2022 artfynd.xlsx
+++ b/artfynd/A 21511-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21511-2022 artfynd.xlsx
+++ b/artfynd/A 21511-2022 artfynd.xlsx
@@ -8300,10 +8300,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119896724</v>
+        <v>119896718</v>
       </c>
       <c r="B68" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8312,20 +8312,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8333,14 +8333,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8349,10 +8345,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>505046</v>
+        <v>505013</v>
       </c>
       <c r="R68" t="n">
-        <v>7024534</v>
+        <v>7024563</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8411,10 +8407,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119896718</v>
+        <v>119896724</v>
       </c>
       <c r="B69" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8423,20 +8419,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8444,10 +8440,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>505013</v>
+        <v>505046</v>
       </c>
       <c r="R69" t="n">
-        <v>7024563</v>
+        <v>7024534</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>

--- a/artfynd/A 21511-2022 artfynd.xlsx
+++ b/artfynd/A 21511-2022 artfynd.xlsx
@@ -8303,7 +8303,7 @@
         <v>119896718</v>
       </c>
       <c r="B68" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>119896724</v>
       </c>
       <c r="B69" t="n">
-        <v>57421</v>
+        <v>57431</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>

--- a/artfynd/A 21511-2022 artfynd.xlsx
+++ b/artfynd/A 21511-2022 artfynd.xlsx
@@ -8521,7 +8521,7 @@
         <v>126817615</v>
       </c>
       <c r="B70" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>126816012</v>
       </c>
       <c r="B72" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>126814929</v>
       </c>
       <c r="B73" t="n">
-        <v>75066</v>
+        <v>75126</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>126816309</v>
       </c>
       <c r="B74" t="n">
-        <v>74886</v>
+        <v>74945</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>126815366</v>
       </c>
       <c r="B75" t="n">
-        <v>79236</v>
+        <v>79267</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>126818779</v>
       </c>
       <c r="B76" t="n">
-        <v>75063</v>
+        <v>75122</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>126817193</v>
       </c>
       <c r="B77" t="n">
-        <v>80043</v>
+        <v>80074</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>126814403</v>
       </c>
       <c r="B78" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>126817187</v>
       </c>
       <c r="B79" t="n">
-        <v>75063</v>
+        <v>75122</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>126816025</v>
       </c>
       <c r="B80" t="n">
-        <v>88654</v>
+        <v>88722</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>126815476</v>
       </c>
       <c r="B82" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>126814444</v>
       </c>
       <c r="B83" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9952,10 +9952,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126842324</v>
+        <v>126840327</v>
       </c>
       <c r="B84" t="n">
-        <v>78980</v>
+        <v>80115</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9963,48 +9963,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Sällflon, Sällflon, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>505090</v>
+        <v>504965</v>
       </c>
       <c r="R84" t="n">
-        <v>7024577</v>
+        <v>7024486</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10041,7 +10027,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Garnlavsrikt, många av bålarna har apotechier</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10068,10 +10054,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126840327</v>
+        <v>126842324</v>
       </c>
       <c r="B85" t="n">
-        <v>80084</v>
+        <v>79011</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10079,34 +10065,48 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Sällflon, Sällflon, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>504965</v>
+        <v>505090</v>
       </c>
       <c r="R85" t="n">
-        <v>7024486</v>
+        <v>7024577</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Garnlavsrikt, många av bålarna har apotechier</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10173,7 +10173,7 @@
         <v>126841646</v>
       </c>
       <c r="B86" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>126842794</v>
       </c>
       <c r="B87" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>126842675</v>
       </c>
       <c r="B88" t="n">
-        <v>80043</v>
+        <v>80074</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>126841619</v>
       </c>
       <c r="B89" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>126842840</v>
       </c>
       <c r="B91" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>126839367</v>
       </c>
       <c r="B92" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>126843092</v>
       </c>
       <c r="B93" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10975,32 +10975,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126839057</v>
+        <v>126842471</v>
       </c>
       <c r="B94" t="n">
-        <v>91245</v>
+        <v>92016</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>504930</v>
+        <v>505131</v>
       </c>
       <c r="R94" t="n">
-        <v>7024360</v>
+        <v>7024517</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11072,32 +11072,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126842471</v>
+        <v>126839057</v>
       </c>
       <c r="B95" t="n">
-        <v>91942</v>
+        <v>91319</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11107,10 +11107,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>505131</v>
+        <v>504930</v>
       </c>
       <c r="R95" t="n">
-        <v>7024517</v>
+        <v>7024360</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11172,7 +11172,7 @@
         <v>126841711</v>
       </c>
       <c r="B96" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11391,10 +11391,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126838679</v>
+        <v>126842129</v>
       </c>
       <c r="B98" t="n">
-        <v>78739</v>
+        <v>91319</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11402,21 +11402,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11426,10 +11426,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>504993</v>
+        <v>505011</v>
       </c>
       <c r="R98" t="n">
-        <v>7024336</v>
+        <v>7024556</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11488,10 +11488,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126842129</v>
+        <v>126838679</v>
       </c>
       <c r="B99" t="n">
-        <v>91245</v>
+        <v>78770</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11499,21 +11499,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11523,10 +11523,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>505011</v>
+        <v>504993</v>
       </c>
       <c r="R99" t="n">
-        <v>7024556</v>
+        <v>7024336</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11585,32 +11585,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126840343</v>
+        <v>126838724</v>
       </c>
       <c r="B100" t="n">
-        <v>80118</v>
+        <v>82852</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11620,10 +11620,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>504974</v>
+        <v>504998</v>
       </c>
       <c r="R100" t="n">
-        <v>7024488</v>
+        <v>7024337</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11685,7 +11685,7 @@
         <v>126842677</v>
       </c>
       <c r="B101" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11779,32 +11779,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126838724</v>
+        <v>126840343</v>
       </c>
       <c r="B102" t="n">
-        <v>82792</v>
+        <v>80149</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11814,10 +11814,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>504998</v>
+        <v>504974</v>
       </c>
       <c r="R102" t="n">
-        <v>7024337</v>
+        <v>7024488</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11987,10 +11987,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126840084</v>
+        <v>126837850</v>
       </c>
       <c r="B104" t="n">
-        <v>80084</v>
+        <v>91319</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11998,21 +11998,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12022,10 +12022,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>504868</v>
+        <v>505143</v>
       </c>
       <c r="R104" t="n">
-        <v>7024448</v>
+        <v>7024072</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12084,10 +12084,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126841448</v>
+        <v>126842846</v>
       </c>
       <c r="B105" t="n">
-        <v>57817</v>
+        <v>80115</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12095,48 +12095,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Sällflon, Sällflon, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>504905</v>
+        <v>505236</v>
       </c>
       <c r="R105" t="n">
-        <v>7024453</v>
+        <v>7024349</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12195,10 +12181,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126842846</v>
+        <v>126840084</v>
       </c>
       <c r="B106" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12230,10 +12216,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>505236</v>
+        <v>504868</v>
       </c>
       <c r="R106" t="n">
-        <v>7024349</v>
+        <v>7024448</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12292,10 +12278,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126837850</v>
+        <v>126840042</v>
       </c>
       <c r="B107" t="n">
-        <v>91245</v>
+        <v>80114</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12303,21 +12289,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12327,10 +12313,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>505143</v>
+        <v>504865</v>
       </c>
       <c r="R107" t="n">
-        <v>7024072</v>
+        <v>7024437</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12363,6 +12349,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12389,10 +12380,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126840042</v>
+        <v>126841448</v>
       </c>
       <c r="B108" t="n">
-        <v>80083</v>
+        <v>57817</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12400,34 +12391,48 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Sällflon, Sällflon, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>504865</v>
+        <v>504905</v>
       </c>
       <c r="R108" t="n">
-        <v>7024437</v>
+        <v>7024453</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12460,11 +12465,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12494,7 +12494,7 @@
         <v>126839650</v>
       </c>
       <c r="B109" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>126842565</v>
       </c>
       <c r="B110" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>126840330</v>
       </c>
       <c r="B111" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
